--- a/data/evaluation/task4/task4_before_after.xlsx
+++ b/data/evaluation/task4/task4_before_after.xlsx
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0.827</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.011</v>
+        <v>0.017</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.8</v>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.927</v>
+        <v>0.929</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>0.912</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.015</v>
+        <v>-0.017</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.95</v>
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.854</v>
+        <v>0.858</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0.825</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.029</v>
+        <v>-0.033</v>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
@@ -761,13 +761,13 @@
         <v>0.913</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.927</v>
+        <v>0.929</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.854</v>
+        <v>0.858</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -795,10 +795,10 @@
         <v>0.803</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.912</v>
+        <v>0.915</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.825</v>
+        <v>0.829</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
@@ -823,13 +823,13 @@
         <v>0.927</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.833</v>
+        <v>0.827</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.917</v>
+        <v>0.919</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.833</v>
+        <v>0.838</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
@@ -857,10 +857,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.925</v>
+        <v>0.927</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.85</v>
+        <v>0.854</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -955,7 +955,7 @@
         <v>0.927</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.804</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.912</v>
@@ -976,10 +976,10 @@
         <v>0.927</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.917</v>
+        <v>0.919</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>0.831</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.912</v>
+        <v>0.915</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -2516,13 +2516,13 @@
         <v>0.8</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>0.833</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="I29" s="2" t="n">
         <v>0.85</v>
@@ -2537,10 +2537,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.167</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="30">
@@ -2804,13 +2804,13 @@
         <v>0.88</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.78</v>
+        <v>0.747</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.787</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.925</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0.887</v>
@@ -2943,7 +2943,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.927 → 优化后 0.912，相对持平），</t>
+          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.929 → 优化后 0.912，相对持平），</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/task4/task4_before_after.xlsx
+++ b/data/evaluation/task4/task4_before_after.xlsx
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.913</v>
+        <v>0.92</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.8</v>
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.893</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.827</v>
+        <v>0.931</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.017</v>
+        <v>0.038</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.8</v>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.929</v>
+        <v>0.885</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.912</v>
+        <v>0.874</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.017</v>
+        <v>-0.012</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.95</v>
@@ -604,10 +604,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.858</v>
+        <v>0.771</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.825</v>
+        <v>0.754</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.033</v>
+        <v>-0.017</v>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
@@ -658,13 +658,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.76</v>
+        <v>1.827</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1.793</v>
+        <v>1.847</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.033</v>
+        <v>0.02</v>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
@@ -758,16 +758,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.913</v>
+        <v>0.92</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.893</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.929</v>
+        <v>0.885</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.858</v>
+        <v>0.771</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -792,13 +792,13 @@
         <v>0.927</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.803</v>
+        <v>0.904</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.915</v>
+        <v>0.892</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.829</v>
+        <v>0.783</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
@@ -820,16 +820,16 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.927</v>
+        <v>0.92</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.827</v>
+        <v>0.908</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.919</v>
+        <v>0.878</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.838</v>
+        <v>0.763</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
@@ -851,16 +851,16 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.913</v>
+        <v>0.9</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.893</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.927</v>
+        <v>0.892</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.854</v>
+        <v>0.783</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -885,13 +885,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.827</v>
+        <v>0.931</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.912</v>
+        <v>0.874</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.825</v>
+        <v>0.754</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.927</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.931</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.912</v>
+        <v>0.874</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.927</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.931</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.919</v>
+        <v>0.884</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.927</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.831</v>
+        <v>0.92</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.915</v>
+        <v>0.876</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.927</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.716</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.908</v>
+        <v>0.761</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.927</v>
+        <v>0.92</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.823</v>
+        <v>0.931</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.915</v>
+        <v>0.874</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.927</v>
+        <v>0.907</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.826</v>
+        <v>0.913</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.923</v>
+        <v>0.874</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -1196,22 +1196,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>1</v>
@@ -1258,10 +1258,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -1296,28 +1296,28 @@
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>0.334</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -1346,15 +1346,15 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.444</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.444</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>4</v>
@@ -1390,10 +1390,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0.75</v>
@@ -1402,7 +1402,7 @@
         <v>0.75</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>3</v>
@@ -1446,10 +1446,10 @@
         <v>1</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>4</v>
@@ -1546,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>0.85</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
@@ -1646,13 +1646,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>5</v>
@@ -1664,7 +1664,7 @@
         <v>0.4</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
@@ -1696,25 +1696,25 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="13">
@@ -1792,10 +1792,10 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="18">
@@ -1978,22 +1978,22 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="19">
@@ -2028,22 +2028,22 @@
         <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.444</v>
+        <v>0.8</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.444</v>
+        <v>0.8</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="20">
@@ -2072,30 +2072,30 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.222</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
     </row>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I21" s="2" t="n">
         <v>0.8</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0.9</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>3</v>
@@ -2143,10 +2143,10 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="22">
@@ -2181,7 +2181,7 @@
         <v>0.9</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>5</v>
@@ -2196,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0.75</v>
@@ -2228,7 +2228,7 @@
         <v>0.75</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0.95</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="24">
@@ -2278,10 +2278,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>5</v>
@@ -2316,37 +2316,37 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>4</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="26">
@@ -2425,7 +2425,7 @@
         <v>0.9</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>4</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="28">
@@ -2516,22 +2516,22 @@
         <v>0.8</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2563,13 +2563,13 @@
         <v>0.6</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
     </row>
@@ -2607,16 +2607,16 @@
         <v>1</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>0.9</v>
@@ -2628,13 +2628,13 @@
         <v>3</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -2714,22 +2714,22 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.777</v>
+        <v>0.867</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.777</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.925</v>
+        <v>0.887</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.925</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="3">
@@ -2742,22 +2742,22 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.917</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.917</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.862</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -2770,10 +2770,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.91</v>
@@ -2782,10 +2782,10 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.919</v>
+        <v>0.906</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.912</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="5">
@@ -2804,16 +2804,16 @@
         <v>0.88</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.747</v>
+        <v>0.794</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.787</v>
+        <v>0.874</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.887</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.887</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="6">
@@ -2826,22 +2826,22 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.617</v>
+        <v>0.96</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.599</v>
+        <v>0.96</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.975</v>
+        <v>0.825</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.975</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2888,7 +2888,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>· 若检索只返回 gold 证据，Entity Precision = 0.329，对应 Entity Accuracy = 0.665</t>
+          <t>· 若检索只返回 gold 证据，Entity Precision = 0.279，对应 Entity Accuracy = 0.640</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.929 → 优化后 0.912，相对持平），</t>
+          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.885 → 优化后 0.874，相对持平），</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/task4/task4_before_after.xlsx
+++ b/data/evaluation/task4/task4_before_after.xlsx
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>0.92</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="D2" s="2" t="n">
-        <v>0.02</v>
+        <v>0.007</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.8</v>
@@ -550,10 +550,10 @@
         <v>0.893</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.931</v>
+        <v>0.92</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.038</v>
+        <v>0.027</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.8</v>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.885</v>
+        <v>0.921</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.874</v>
+        <v>0.892</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.012</v>
+        <v>-0.029</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.95</v>
@@ -604,10 +604,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.771</v>
+        <v>0.842</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.754</v>
+        <v>0.783</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.017</v>
+        <v>-0.058</v>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
@@ -661,10 +661,10 @@
         <v>1.827</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1.847</v>
+        <v>1.827</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
@@ -758,16 +758,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.913</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.893</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.885</v>
+        <v>0.921</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.771</v>
+        <v>0.842</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -789,16 +789,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.927</v>
+        <v>0.913</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.904</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.892</v>
+        <v>0.919</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.783</v>
+        <v>0.838</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
@@ -820,16 +820,16 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>0.92</v>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>0.908</v>
-      </c>
       <c r="G4" s="2" t="n">
-        <v>0.878</v>
+        <v>0.894</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.763</v>
+        <v>0.787</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
@@ -851,16 +851,16 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9</v>
+        <v>0.907</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.893</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.892</v>
+        <v>0.917</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.783</v>
+        <v>0.833</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -882,16 +882,16 @@
         <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.931</v>
+        <v>0.92</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.874</v>
+        <v>0.892</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.754</v>
+        <v>0.783</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.931</v>
+        <v>0.92</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.874</v>
+        <v>0.892</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.913</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.931</v>
+        <v>0.908</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.884</v>
+        <v>0.9</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.927</v>
+        <v>0.913</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.876</v>
+        <v>0.892</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.927</v>
+        <v>0.873</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.681</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.761</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>0.92</v>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>0.931</v>
-      </c>
       <c r="D6" s="2" t="n">
-        <v>0.874</v>
+        <v>0.894</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.907</v>
+        <v>0.887</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.913</v>
+        <v>0.908</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.874</v>
+        <v>0.925</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -1202,10 +1202,10 @@
         <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4</v>
@@ -1299,13 +1299,13 @@
         <v>0.333</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.334</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0.75</v>
@@ -1405,7 +1405,7 @@
         <v>4</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="7">
@@ -1446,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0.95</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="8">
@@ -1546,16 +1546,16 @@
         <v>1</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>0.85</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="10">
@@ -1649,13 +1649,13 @@
         <v>0.9</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1664,7 +1664,7 @@
         <v>0.4</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="12">
@@ -1934,10 +1934,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>2</v>
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.017</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="18">
@@ -1984,7 +1984,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>0.85</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="19">
@@ -2034,16 +2034,16 @@
         <v>0.8</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -2128,13 +2128,13 @@
         <v>1</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>3</v>
@@ -2146,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="22">
@@ -2178,10 +2178,10 @@
         <v>1</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>5</v>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0.75</v>
@@ -2228,7 +2228,7 @@
         <v>0.75</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0.95</v>
@@ -2240,13 +2240,13 @@
         <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="24">
@@ -2328,7 +2328,7 @@
         <v>0.833</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>0.85</v>
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
@@ -2380,10 +2380,10 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0.8</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0.8</v>
@@ -2422,7 +2422,7 @@
         <v>0.8</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I27" s="2" t="n">
         <v>0.95</v>
@@ -2434,13 +2434,13 @@
         <v>4</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2475,7 +2475,7 @@
         <v>0.95</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>4</v>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2510,28 +2510,28 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="I29" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="F29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0.75</v>
-      </c>
       <c r="J29" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>0.8</v>
@@ -2580,7 +2580,7 @@
         <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>0.4</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>0.8</v>
@@ -2619,22 +2619,22 @@
         <v>0.95</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2723,13 +2723,13 @@
         <v>0.867</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.887</v>
+        <v>0.925</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.887</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="3">
@@ -2742,10 +2742,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.917</v>
@@ -2754,10 +2754,10 @@
         <v>0.917</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.925</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="4">
@@ -2782,10 +2782,10 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.906</v>
+        <v>0.925</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.881</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="5">
@@ -2798,7 +2798,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.88</v>
@@ -2810,10 +2810,10 @@
         <v>0.874</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.887</v>
+        <v>0.912</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.875</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="6">
@@ -2838,10 +2838,10 @@
         <v>0.96</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.825</v>
+        <v>0.912</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.838</v>
       </c>
     </row>
   </sheetData>
@@ -2943,7 +2943,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.885 → 优化后 0.874，相对持平），</t>
+          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.921 → 优化后 0.892，相对持平），</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/task4/task4_before_after.xlsx
+++ b/data/evaluation/task4/task4_before_after.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Metric Notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Per Question'!$A$1:$N$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Per Question'!$A$1:$N$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.913</v>
+        <v>0.8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.835</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.007</v>
+        <v>0.035</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.8</v>
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.893</v>
+        <v>0.916</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.92</v>
+        <v>0.919</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.027</v>
+        <v>0.003</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.8</v>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.921</v>
+        <v>0.93</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.892</v>
+        <v>0.92</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.029</v>
+        <v>-0.011</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.95</v>
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.842</v>
+        <v>0.861</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.783</v>
+        <v>0.839</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.058</v>
+        <v>-0.021</v>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
@@ -658,13 +658,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.827</v>
+        <v>1.86</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1.827</v>
+        <v>1.87</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
@@ -758,16 +758,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.913</v>
+        <v>0.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.893</v>
+        <v>0.916</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.921</v>
+        <v>0.93</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.842</v>
+        <v>0.861</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -789,16 +789,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.913</v>
+        <v>0.805</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.904</v>
+        <v>0.907</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.919</v>
+        <v>0.914</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.838</v>
+        <v>0.827</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
@@ -820,16 +820,16 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.907</v>
+        <v>0.83</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.927</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.894</v>
+        <v>0.9</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.787</v>
+        <v>0.8</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
@@ -851,16 +851,16 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.907</v>
+        <v>0.795</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.893</v>
+        <v>0.916</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.917</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.833</v>
+        <v>0.864</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -882,16 +882,16 @@
         <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>0.92</v>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.892</v>
-      </c>
       <c r="H6" s="2" t="n">
-        <v>0.783</v>
+        <v>0.839</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.915</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.892</v>
+        <v>0.909</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.913</v>
+        <v>0.805</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.908</v>
+        <v>0.89</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.921</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.913</v>
+        <v>0.835</v>
       </c>
       <c r="C4" s="2" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>0.92</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.892</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.873</v>
+        <v>0.795</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.681</v>
+        <v>0.752</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.892</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.893</v>
+        <v>0.8</v>
       </c>
       <c r="C6" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>0.92</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.894</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.887</v>
+        <v>0.785</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.908</v>
+        <v>0.905</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.925</v>
+        <v>0.921</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1202,16 +1202,16 @@
         <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -1243,19 +1243,19 @@
         <v>0.6</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2</v>
@@ -1264,13 +1264,13 @@
         <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0</v>
+        <v>-0.333</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="4">
@@ -1302,7 +1302,7 @@
         <v>0.333</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>0.95</v>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="5">
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -1399,13 +1399,13 @@
         <v>0.8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="7">
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>4</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -1496,10 +1496,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>4</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1546,13 +1546,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>4</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1596,10 +1596,10 @@
         <v>1</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>4</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -1649,7 +1649,7 @@
         <v>0.9</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>3</v>
@@ -1658,13 +1658,13 @@
         <v>4</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
@@ -1696,10 +1696,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>3</v>
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1887,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>2</v>
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
@@ -1934,10 +1934,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>2</v>
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1984,7 +1984,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>0.85</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0.8</v>
@@ -2034,25 +2034,25 @@
         <v>0.8</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>0.85</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2075,24 +2075,24 @@
         <v>0.8</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -2128,16 +2128,16 @@
         <v>1</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -2146,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2178,16 +2178,16 @@
         <v>1</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
         <v>0.75</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0.95</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2278,10 +2278,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>5</v>
@@ -2328,10 +2328,10 @@
         <v>0.833</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>4</v>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
@@ -2380,10 +2380,10 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0.8</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>4</v>
@@ -2472,10 +2472,10 @@
         <v>1</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>4</v>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0.6</v>
@@ -2616,10 +2616,10 @@
         <v>0.571</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>2</v>
@@ -2637,8 +2637,502 @@
         <v>0</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>-0.333</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N31"/>
+  <autoFilter ref="A1:N41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2711,25 +3205,25 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.825</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.867</v>
+        <v>0.917</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.867</v>
+        <v>0.833</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.925</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.912</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="3">
@@ -2739,25 +3233,25 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.88</v>
+        <v>0.857</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.88</v>
+        <v>0.886</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.917</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.917</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.925</v>
+        <v>0.967</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.912</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="4">
@@ -2767,25 +3261,25 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.91</v>
+        <v>0.925</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.95</v>
+        <v>0.958</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.925</v>
+        <v>0.915</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.887</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="5">
@@ -2795,25 +3289,25 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.88</v>
+        <v>0.833</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.794</v>
+        <v>0.829</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.874</v>
+        <v>0.895</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.912</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.912</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2823,25 +3317,25 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.96</v>
+        <v>0.743</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.96</v>
+        <v>0.948</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.96</v>
+        <v>0.948</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.912</v>
+        <v>0.9</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.838</v>
+        <v>0.875</v>
       </c>
     </row>
   </sheetData>
@@ -2881,21 +3375,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>· 含实体问题数：24（Q004/Q012/Q013/Q019/Q025/Q029 无实体，不计入）</t>
+          <t>· 含实体问题数：33（Q004/Q012/Q013/Q019/Q025/Q029 无实体，不计入）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>· 若检索只返回 gold 证据，Entity Precision = 0.279，对应 Entity Accuracy = 0.640</t>
+          <t>· 若检索只返回 gold 证据，Entity Precision = 0.248，对应 Entity Accuracy = 0.624</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>· 语料可达的 Entity Precision 上限 = 0.963（对应 Entity Accuracy ≈ 0.981）</t>
+          <t>· 语料可达的 Entity Precision 上限 = 0.973（对应 Entity Accuracy ≈ 0.986）</t>
         </is>
       </c>
     </row>
@@ -2943,7 +3437,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.921 → 优化后 0.892，相对持平），</t>
+          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.930 → 优化后 0.920，相对持平），</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/task4/task4_before_after.xlsx
+++ b/data/evaluation/task4/task4_before_after.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Metric Notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Per Question'!$A$1:$N$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Per Question'!$A$1:$N$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0.835</v>
-      </c>
       <c r="D2" s="2" t="n">
-        <v>0.035</v>
+        <v>0.023</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.8</v>
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.916</v>
+        <v>0.921</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.919</v>
+        <v>0.925</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.003</v>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.93</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.011</v>
+        <v>-0.013</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.95</v>
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.861</v>
+        <v>0.867</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.839</v>
+        <v>0.842</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.021</v>
+        <v>-0.025</v>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
@@ -661,10 +661,10 @@
         <v>1.86</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1.87</v>
+        <v>1.874</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
@@ -758,16 +758,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.8</v>
+        <v>0.777</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.916</v>
+        <v>0.921</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.93</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.861</v>
+        <v>0.867</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -789,16 +789,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.805</v>
+        <v>0.772</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.907</v>
+        <v>0.914</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.914</v>
+        <v>0.921</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.827</v>
+        <v>0.842</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
@@ -820,16 +820,16 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.83</v>
+        <v>0.805</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.927</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9</v>
+        <v>0.904</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
@@ -851,16 +851,16 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.795</v>
+        <v>0.772</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.916</v>
+        <v>0.921</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.864</v>
+        <v>0.869</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -882,16 +882,16 @@
         <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.835</v>
+        <v>0.8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.919</v>
+        <v>0.925</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.839</v>
+        <v>0.842</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.85</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="C2" s="2" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>0.915</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.909</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.805</v>
+        <v>0.781</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.89</v>
+        <v>0.897</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.921</v>
+        <v>0.922</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.835</v>
+        <v>0.8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.919</v>
+        <v>0.925</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.795</v>
+        <v>0.781</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.752</v>
+        <v>0.785</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.892</v>
+        <v>0.906</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.8</v>
+        <v>0.777</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.91</v>
+        <v>0.916</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.785</v>
+        <v>0.758</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.905</v>
+        <v>0.911</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.921</v>
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3001,7 +3001,7 @@
         <v>0.6</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>1</v>
@@ -3010,10 +3010,10 @@
         <v>1</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>1</v>
@@ -3022,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>0.6</v>
@@ -3063,22 +3063,22 @@
         <v>0.95</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="41">
@@ -3131,8 +3131,158 @@
         <v>0</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N41"/>
+  <autoFilter ref="A1:N44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3233,25 +3383,25 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.857</v>
+        <v>0.8</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.886</v>
+        <v>0.8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.948</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.948</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.967</v>
+        <v>0.957</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.958</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -3261,25 +3411,25 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.757</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.85</v>
+        <v>0.786</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.958</v>
+        <v>0.964</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.915</v>
+        <v>0.929</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.93</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3320,7 +3470,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.714</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.743</v>
@@ -3335,7 +3485,7 @@
         <v>0.9</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.875</v>
+        <v>0.883</v>
       </c>
     </row>
   </sheetData>
@@ -3375,21 +3525,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>· 含实体问题数：33（Q004/Q012/Q013/Q019/Q025/Q029 无实体，不计入）</t>
+          <t>· 含实体问题数：36（Q004/Q012/Q013/Q019/Q025/Q029 无实体，不计入）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>· 若检索只返回 gold 证据，Entity Precision = 0.248，对应 Entity Accuracy = 0.624</t>
+          <t>· 若检索只返回 gold 证据，Entity Precision = 0.239，对应 Entity Accuracy = 0.619</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>· 语料可达的 Entity Precision 上限 = 0.973（对应 Entity Accuracy ≈ 0.986）</t>
+          <t>· 语料可达的 Entity Precision 上限 = 0.975（对应 Entity Accuracy ≈ 0.988）</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3587,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.930 → 优化后 0.920，相对持平），</t>
+          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.933 → 优化后 0.921，相对持平），</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/task4/task4_before_after.xlsx
+++ b/data/evaluation/task4/task4_before_after.xlsx
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.777</v>
+        <v>0.772</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.023</v>
+        <v>0.028</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.8</v>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.013</v>
+        <v>-0.015</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.95</v>
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.867</v>
+        <v>0.869</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.842</v>
+        <v>0.839</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.025</v>
+        <v>-0.031</v>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
@@ -758,16 +758,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.777</v>
+        <v>0.772</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.921</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.867</v>
+        <v>0.869</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -789,16 +789,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.772</v>
+        <v>0.777</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.914</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.921</v>
+        <v>0.922</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.842</v>
+        <v>0.844</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
@@ -826,10 +826,10 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.904</v>
+        <v>0.903</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
@@ -857,10 +857,10 @@
         <v>0.921</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.869</v>
+        <v>0.872</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -888,10 +888,10 @@
         <v>0.925</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.842</v>
+        <v>0.839</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.8</v>
+        <v>0.805</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>0.925</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.781</v>
+        <v>0.777</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0.785</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.906</v>
+        <v>0.904</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.777</v>
+        <v>0.781</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0.916</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.921</v>
+        <v>0.922</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>0.758</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.911</v>
+        <v>0.916</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.921</v>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E19" s="2" t="n">
         <v>0.8</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0.6</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0.8</v>
@@ -2046,7 +2046,7 @@
         <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>0.8</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>1</v>
@@ -2774,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>0</v>
@@ -2860,10 +2860,10 @@
         <v>1</v>
       </c>
       <c r="H36" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I36" s="2" t="n">
         <v>0.7</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0.75</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>2</v>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="37">
@@ -3361,7 +3361,7 @@
         <v>0.825</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.85</v>
+        <v>0.825</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.917</v>
@@ -3426,10 +3426,10 @@
         <v>0.964</v>
       </c>
       <c r="G4" s="2" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>0.929</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3470,10 +3470,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.714</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.743</v>
+        <v>0.771</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.948</v>
@@ -3587,7 +3587,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.933 → 优化后 0.921，相对持平），</t>
+          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.935 → 优化后 0.919，相对持平），</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/task4/task4_before_after.xlsx
+++ b/data/evaluation/task4/task4_before_after.xlsx
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.772</v>
+        <v>0.763</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.8</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.028</v>
+        <v>0.051</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.8</v>
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.921</v>
+        <v>0.905</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.925</v>
+        <v>0.907</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.8</v>
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.919</v>
+        <v>0.921</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>-0.015</v>
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.869</v>
+        <v>0.872</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.839</v>
+        <v>0.842</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>-0.031</v>
@@ -658,13 +658,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1.874</v>
+        <v>1.888</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
@@ -758,16 +758,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.772</v>
+        <v>0.763</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.921</v>
+        <v>0.905</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.869</v>
+        <v>0.872</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -789,16 +789,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.777</v>
+        <v>0.772</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.914</v>
+        <v>0.909</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.922</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.844</v>
+        <v>0.878</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
@@ -820,16 +820,16 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.805</v>
+        <v>0.791</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.914</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.903</v>
+        <v>0.906</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.806</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
@@ -851,10 +851,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.772</v>
+        <v>0.758</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.921</v>
+        <v>0.913</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.9360000000000001</v>
@@ -882,16 +882,16 @@
         <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.925</v>
+        <v>0.907</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.919</v>
+        <v>0.921</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.839</v>
+        <v>0.842</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.921</v>
+        <v>0.896</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.915</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.781</v>
+        <v>0.795</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.897</v>
+        <v>0.88</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.922</v>
+        <v>0.924</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -997,10 +997,10 @@
         <v>0.805</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.925</v>
+        <v>0.901</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.919</v>
+        <v>0.922</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.777</v>
+        <v>0.795</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.785</v>
+        <v>0.776</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.904</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.781</v>
+        <v>0.786</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.916</v>
+        <v>0.898</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.922</v>
+        <v>0.924</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.758</v>
+        <v>0.753</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.916</v>
+        <v>0.902</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.921</v>
+        <v>0.925</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>0.9</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="3">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.8</v>
@@ -1255,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2</v>
@@ -1264,13 +1264,13 @@
         <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-0.333</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="4">
@@ -1399,10 +1399,10 @@
         <v>0.8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>3</v>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="7">
@@ -1496,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -1546,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>0.95</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="10">
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>1</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="11">
@@ -1646,7 +1646,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>1</v>
@@ -1664,7 +1664,7 @@
         <v>0.4</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="12">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
@@ -1696,16 +1696,16 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0.5</v>
@@ -1928,7 +1928,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1</v>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>0.85</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>4</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="19">
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>0.85</v>
@@ -2146,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="22">
@@ -2178,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>1</v>
@@ -2196,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="23">
@@ -2228,7 +2228,7 @@
         <v>0.75</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0.95</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="24">
@@ -2278,13 +2278,13 @@
         <v>1</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0.95</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>5</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="25">
@@ -2328,7 +2328,7 @@
         <v>0.833</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>0.9</v>
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="26">
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0.8</v>
@@ -2434,7 +2434,7 @@
         <v>4</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>1</v>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="29">
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
@@ -2522,16 +2522,16 @@
         <v>1</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="I29" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="30">
@@ -2569,7 +2569,7 @@
         <v>0.6</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2577,13 +2577,13 @@
         <v>3</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
     </row>
@@ -2616,7 +2616,7 @@
         <v>0.571</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>1</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="32">
@@ -2666,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>0.9</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="33">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E34" s="2" t="n">
         <v>0.8</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0.6</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>1</v>
@@ -2774,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>0.95</v>
@@ -2828,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>0.8</v>
@@ -2922,7 +2922,7 @@
         <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>0</v>
@@ -2998,11 +2998,11 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E39" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>0.4</v>
-      </c>
       <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>0.9</v>
@@ -3078,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="41">
@@ -3160,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>0.85</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="43">
@@ -3210,7 +3210,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>0.9</v>
@@ -3228,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="44">
@@ -3358,10 +3358,10 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.825</v>
+        <v>0.775</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.825</v>
+        <v>0.85</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.917</v>
@@ -3373,7 +3373,7 @@
         <v>0.9419999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.892</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="3">
@@ -3386,19 +3386,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.725</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.948</v>
+        <v>0.923</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.948</v>
+        <v>0.923</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.957</v>
+        <v>0.95</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0.9429999999999999</v>
@@ -3414,10 +3414,10 @@
         <v>14</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.757</v>
+        <v>0.786</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.786</v>
+        <v>0.843</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.9360000000000001</v>
@@ -3426,10 +3426,10 @@
         <v>0.964</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.946</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.929</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3445,16 +3445,16 @@
         <v>0.8</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0.829</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.895</v>
+        <v>0.829</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0.9399999999999999</v>
@@ -3470,22 +3470,22 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.714</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.771</v>
+        <v>0.8</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.948</v>
+        <v>0.876</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.948</v>
+        <v>0.924</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9</v>
+        <v>0.917</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.883</v>
+        <v>0.892</v>
       </c>
     </row>
   </sheetData>
@@ -3587,7 +3587,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.935 → 优化后 0.919，相对持平），</t>
+          <t>本次把 Entity Accuracy 作为**不劣化约束**（baseline 0.936 → 优化后 0.921，相对持平），</t>
         </is>
       </c>
     </row>
